--- a/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92994023743</v>
+        <v>46157.9308160716</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9308160716</v>
+        <v>46157.93352418913</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93352418913</v>
+        <v>46157.93639689047</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93639689047</v>
+        <v>46158.28177481121</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28177481121</v>
+        <v>46158.29754087618</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46157.92957225287</v>
+        <v>46158.2971601284</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         <v>0.01</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>46157.92957225287</v>
+        <v>46158.2971601284</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>46157.92957225287</v>
+        <v>46158.2971601284</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29754087618</v>
+        <v>46158.29772238414</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29772238414</v>
+        <v>46158.30446337426</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.30446337426</v>
+        <v>46158.33341136375</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33341136375</v>
+        <v>46158.37201892422</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37201892422</v>
+        <v>46158.37417198664</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -724,7 +724,7 @@
         <v>6.7</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46158.2971601284</v>
+        <v>46158.37371913368</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         <v>0.01</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>46158.2971601284</v>
+        <v>46158.37371913368</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>46158.2971601284</v>
+        <v>46158.37371913368</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
